--- a/AAII_Financials/Quarterly/GOEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOEV_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>GOEV</t>
   </si>
@@ -656,108 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>500</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -790,11 +794,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>2600</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -813,13 +817,16 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>500</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -851,12 +858,12 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -875,13 +882,16 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
@@ -913,12 +923,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3">
         <v>1900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,8 +947,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,56 +974,57 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E12" s="3">
         <v>38600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>47100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>44200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>57100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>115500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>82500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>88200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>59400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>57600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>39300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>90000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19300</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,34 +1102,37 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>26700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
@@ -1120,15 +1140,15 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-5000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,8 +1158,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1147,34 +1167,37 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4600</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
         <v>4600</v>
       </c>
       <c r="F15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G15" s="3">
         <v>2500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2600</v>
-      </c>
-      <c r="K15" s="3">
-        <v>2100</v>
       </c>
       <c r="L15" s="3">
         <v>2100</v>
@@ -1183,25 +1206,25 @@
         <v>2100</v>
       </c>
       <c r="N15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O15" s="3">
         <v>1900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1700</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E17" s="3">
         <v>74500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>108300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>83700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>113400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>173500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>140800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>141500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>107000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>104300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>97100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>127700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-51400</v>
       </c>
       <c r="E18" s="3">
+        <v>-74500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-108300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-83700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-113400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-173500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-140800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-141500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-107000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-104300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-97100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-127700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-22100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-25100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,118 +1411,122 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-60600</v>
       </c>
       <c r="E20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F20" s="3">
         <v>17500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>15400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>26100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>81800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>118500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-110500</v>
       </c>
       <c r="E21" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-86200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-77700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-114300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-161500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-122700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-135500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-78800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-110500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-13100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-29200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1502,8 +1539,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1537,15 +1577,15 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>1100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1555,8 +1595,8 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1564,70 +1604,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-70900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-90700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-80200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-117700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-164400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-125400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-138100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-80900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-112600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1674,22 +1720,25 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
-      </c>
-      <c r="S24" s="3">
-        <v>400</v>
       </c>
       <c r="T24" s="3">
         <v>400</v>
       </c>
       <c r="U24" s="3">
+        <v>400</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-70900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-90700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-80200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-117700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-164400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-125400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-138100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-80900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-112600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-70900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-90700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-80200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-117700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-164400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-125400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-138100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-80900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-112600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2189,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>60600</v>
       </c>
       <c r="E32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-17500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-15400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-26100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-81800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-118500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-70900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-90700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-80200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-117700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-164400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-125400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-138100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-80900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-112600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-70900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-90700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-80200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-117700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-164400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-125400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-138100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-80900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-112600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,70 +2571,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E41" s="3">
         <v>5000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>104900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>224700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>414900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>563600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>641900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>702400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1800</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,8 +2699,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2671,26 +2764,29 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E44" s="3">
         <v>5300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1300</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2706,8 +2802,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2733,46 +2829,49 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15200</v>
+        <v>18800</v>
       </c>
       <c r="E45" s="3">
         <v>15200</v>
       </c>
       <c r="F45" s="3">
+        <v>15200</v>
+      </c>
+      <c r="G45" s="3">
         <v>12800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>36800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>66600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
@@ -2792,73 +2891,79 @@
       <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>100</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E46" s="3">
         <v>25500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>40400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>70600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>142700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>291300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>430900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>576900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>657600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>708900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2892,74 +2997,77 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>306600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>308800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>309200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>307300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>306400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>305000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>303700</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>405600</v>
+      </c>
+      <c r="E48" s="3">
         <v>400600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>367700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>350700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>330400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>302000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>250600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>216500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>155400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>103200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>59300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2972,8 +3080,8 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2981,8 +3089,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,55 +3284,58 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E52" s="3">
         <v>96000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>93400</v>
       </c>
       <c r="F52" s="3">
         <v>93400</v>
       </c>
       <c r="G52" s="3">
+        <v>93400</v>
+      </c>
+      <c r="H52" s="3">
         <v>73900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3414,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>534300</v>
+      </c>
+      <c r="E54" s="3">
         <v>522100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>488100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>496500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>444800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>397500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>420000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>523100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>614500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>711500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>717800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>753500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>307000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>309500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>310100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>308500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>307800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>306600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>305700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,56 +3531,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E57" s="3">
         <v>84400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>88800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>103200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>96600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>93600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>80900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>52300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>63300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>51800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17200</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
       <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
@@ -3458,31 +3589,34 @@
         <v>0</v>
       </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E58" s="3">
         <v>32600</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>34800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12500</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3498,8 +3632,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3525,141 +3659,150 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E59" s="3">
         <v>85300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>85900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>80300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>74100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>86100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>52000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>64500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2700</v>
-      </c>
-      <c r="R59" s="3">
-        <v>2200</v>
       </c>
       <c r="S59" s="3">
         <v>2200</v>
       </c>
       <c r="T59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>187600</v>
+      </c>
+      <c r="E60" s="3">
         <v>202400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>174800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>218300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>183200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>179700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>132900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>136200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>106700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>116200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E61" s="3">
         <v>24000</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -3682,13 +3825,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>6900</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3711,46 +3854,49 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E62" s="3">
         <v>63000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>61600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>41600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>29400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>46400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>72000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>64200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>153400</v>
-      </c>
-      <c r="O62" s="3">
-        <v>10200</v>
       </c>
       <c r="P62" s="3">
         <v>10200</v>
@@ -3770,11 +3916,14 @@
       <c r="U62" s="3">
         <v>10200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4114,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>368700</v>
+      </c>
+      <c r="E66" s="3">
         <v>289400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>236400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>259900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>216900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>209200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>172300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>179100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>153100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>188300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>107600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>188200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10400</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4464,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1453400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1341400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1270600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1179800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1099600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-981900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-817500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-692100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-554000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-473100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-360600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-345400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>300</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4724,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>165700</v>
+      </c>
+      <c r="E76" s="3">
         <v>232700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>251800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>236600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>227900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>188300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>247700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>344000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>461500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>523200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>610300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>565200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>291700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>296700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>297100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>296100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>295400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>296300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>295200</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-70900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-90700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-80200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-117700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-164400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-125400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-138100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-80900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-112600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,34 +5016,35 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4600</v>
+        <v>1500</v>
       </c>
       <c r="E83" s="3">
         <v>4600</v>
       </c>
       <c r="F83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G83" s="3">
         <v>2500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2100</v>
       </c>
       <c r="L83" s="3">
         <v>2100</v>
@@ -4853,26 +5052,26 @@
       <c r="M83" s="3">
         <v>2100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>2100</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4880,8 +5079,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-61900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-62300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-67200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-70600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-92300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-117200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-120300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-120200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-71800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-54900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-53900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-105800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-600</v>
       </c>
       <c r="S89" s="3">
         <v>-600</v>
       </c>
       <c r="T89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,61 +5496,62 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-37000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-62600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-45300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12100</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5338,8 +5559,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-37000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-62600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-71500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S94" s="3">
         <v>400</v>
       </c>
       <c r="T94" s="3">
+        <v>400</v>
+      </c>
+      <c r="U94" s="3">
         <v>500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-303200</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,56 +6039,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E100" s="3">
         <v>76100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>109200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>88600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>83200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>789700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-34400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>17300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>15000</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -5853,13 +6099,16 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>305100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-29600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>30100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-71000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-108900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-188800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-147300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-78400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-60500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>673700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-200</v>
       </c>
       <c r="S102" s="3">
         <v>-200</v>
       </c>
       <c r="T102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1800</v>
       </c>
-      <c r="V102" s="3" t="s">
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>GOEV</t>
   </si>
@@ -656,119 +656,126 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>400</v>
+      </c>
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
@@ -797,14 +804,14 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>2600</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
@@ -820,20 +827,26 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,15 +874,15 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,19 +898,25 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -926,15 +945,15 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>1900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -950,8 +969,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,62 +1000,64 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>31500</v>
+      </c>
+      <c r="F12" s="3">
         <v>22000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>38600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>47100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>44200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>57100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>115500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>82500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>88200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>59400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>57600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>39300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>90000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>18900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>14600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>19300</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1040,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,138 +1138,156 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>26700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>4100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F15" s="3">
         <v>1500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>4600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>4600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>2500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>3400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>2900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2600</v>
-      </c>
-      <c r="L15" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2100</v>
       </c>
       <c r="N15" s="3">
         <v>2100</v>
       </c>
       <c r="O15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1900</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1800</v>
       </c>
       <c r="R15" s="3">
         <v>1700</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="S15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1308,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>64800</v>
+      </c>
+      <c r="F17" s="3">
         <v>51900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>74500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>108300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>83700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>113400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>173500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>140800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>141500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>107000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>104300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>97100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>127700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>24700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>19800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>25100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-51400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-74500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-108300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-83700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-113400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-173500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-140800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-141500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-107000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-104300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-97100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-127700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-19800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-25100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,127 +1477,135 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>35900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-60600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>3600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>17500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-4300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>9100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>15400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>26100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-8200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>81800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>118500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-5800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-110500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-66300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-86200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-77700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-114300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-161500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-122700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-135500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-78800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-110500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-13100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-21500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-29200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1542,31 +1615,37 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1580,100 +1659,112 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>1100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-110700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-112000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-70900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-90700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-80200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-117700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-164400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-125400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-138100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-80900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-112600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-15200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-9200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-23200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-30900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1723,22 +1814,28 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1899,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-110700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-112000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-70900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-90700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-80200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-117700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-164400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-125400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-138100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-80900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-112600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-15200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-9200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-23200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-30900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-111500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-70900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-90700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-80200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-117700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-164400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-125400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-138100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-80900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-112600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-15200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-9200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-23200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-30900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2183,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,138 +2325,156 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="F32" s="3">
         <v>60600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-3600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-17500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>4300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-9100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-15400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-26100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>8200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-81800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-118500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>5800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-111500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-70900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-90700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-80200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-117700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-164400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-125400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-138100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-80900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-112600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-15200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-9200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-23200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-30900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2538,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-111500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-70900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-90700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-80200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-117700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-164400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-125400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-138100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-80900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-112600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-15200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-9200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-23200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-30900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2743,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F41" s="3">
         <v>8300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>36600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>33800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>104900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>224700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>414900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>563600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>641900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>702400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1800</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,8 +2881,14 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2767,32 +2952,38 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F44" s="3">
         <v>5700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>5100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2805,11 +2996,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2832,52 +3023,58 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F45" s="3">
         <v>18800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>15200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>15200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>12800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>32300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>36800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>37800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>66600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>16000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>13300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>15600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>6500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
@@ -2894,76 +3091,88 @@
       <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>100</v>
+      </c>
+      <c r="X45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>32600</v>
+      </c>
+      <c r="F46" s="3">
         <v>32800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>25500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>27000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>52300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>40400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>70600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>142700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>291300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>430900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>576900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>657600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>708900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3000,80 +3209,86 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>306600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>308800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>309200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>307300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>306400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>305000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>303700</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>416100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>413300</v>
+      </c>
+      <c r="F48" s="3">
         <v>405600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>400600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>367700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>350700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>330400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>302000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>250600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>216500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>155400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>103200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>59300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>43300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,17 +3298,23 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3157,8 +3378,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,61 +3520,67 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>96100</v>
+      </c>
+      <c r="F52" s="3">
         <v>95900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>96000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>93400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>93400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>73900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>24900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>26700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>15200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>28300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>31400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3352,8 +3591,14 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3662,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>544700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>542000</v>
+      </c>
+      <c r="F54" s="3">
         <v>534300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>522100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>488100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>496500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>444800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>397500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>420000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>523100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>614500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>711500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>717800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>753500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>307000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>309500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>310100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>308500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>307800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>306600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>305700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,97 +3791,105 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>65300</v>
+      </c>
+      <c r="F57" s="3">
         <v>78000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>84400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>88800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>103200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>96600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>93600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>80900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>52300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>63300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>51800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>17800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>17200</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
       <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>54400</v>
+      </c>
+      <c r="F58" s="3">
         <v>45600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>32600</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>34800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>12500</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3635,11 +3902,11 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3662,153 +3929,171 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>64800</v>
+      </c>
+      <c r="F59" s="3">
         <v>63900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>85300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>85900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>80300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>74100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>86100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>52000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>83900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>43400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>64500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>18600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>10600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>201200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>184400</v>
+      </c>
+      <c r="F60" s="3">
         <v>187600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>202400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>174800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>218300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>183200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>179700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>132900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>136200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>106700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>116200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>36400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>27900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>5100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>44800</v>
+        <v>28800</v>
       </c>
       <c r="E61" s="3">
+        <v>28900</v>
+      </c>
+      <c r="F61" s="3">
+        <v>68700</v>
+      </c>
+      <c r="G61" s="3">
         <v>24000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -3828,17 +4113,17 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>6900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3857,52 +4142,58 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>136200</v>
+        <v>130400</v>
       </c>
       <c r="E62" s="3">
+        <v>79100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>112300</v>
+      </c>
+      <c r="G62" s="3">
         <v>63000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>61600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>41600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>33700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>29400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>39400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>42900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>46400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>72000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>64200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>153400</v>
-      </c>
-      <c r="P62" s="3">
-        <v>10200</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>10200</v>
       </c>
       <c r="R62" s="3">
         <v>10200</v>
@@ -3919,11 +4210,17 @@
       <c r="V62" s="3">
         <v>10200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="X62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4426,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>360400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>292400</v>
+      </c>
+      <c r="F66" s="3">
         <v>368700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>289400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>236400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>259900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>216900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>209200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>172300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>179100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>153100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>188300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>107600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>188200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>15200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>12900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>12500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>12400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>10300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>10400</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,16 +4666,22 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -4402,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4808,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1592500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1481800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1453400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1341400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1270600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1179800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1099600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-981900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-817500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-692100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-554000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-473100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-360600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-345400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +5092,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>177800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>244000</v>
+      </c>
+      <c r="F76" s="3">
         <v>165700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>232700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>251800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>236600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>227900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>188300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>247700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>344000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>461500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>523200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>610300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>565200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>291700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>296700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>297100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>296100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>295400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>296300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>295200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5234,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-111500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-70900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-90700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-80200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-117700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-164400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-125400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-138100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-80900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-112600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-15200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-9200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-23200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-30900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,73 +5412,81 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>4600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>4600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2600</v>
-      </c>
-      <c r="L83" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>2100</v>
       </c>
       <c r="N83" s="3">
         <v>2100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="O83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>1800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1700</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,52 +5834,58 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-61900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-62300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-67200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-70600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-92300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-117200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-120300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-120200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-71800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-54900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-53900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-105800</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-600</v>
       </c>
       <c r="R89" s="3">
         <v>-300</v>
@@ -5461,19 +5894,25 @@
         <v>-600</v>
       </c>
       <c r="T89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W89" s="3">
         <v>-800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,73 +5936,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-11500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-15500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-18400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-8500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-23400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-37000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-28400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-62600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-45300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-16500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-12100</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +6145,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-11500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-15500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-18400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-8500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-23400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-37000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-62600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-71500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-16500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-12100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-10200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>400</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
       </c>
       <c r="S94" s="3">
         <v>400</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
+        <v>400</v>
+      </c>
+      <c r="W94" s="3">
         <v>500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-303200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6247,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6527,85 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>79600</v>
+      </c>
+      <c r="F100" s="3">
         <v>76700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>76100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>56100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>109200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>88600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>83200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>9500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-6000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-4000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-6900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>5600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>789700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-34400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>17300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>15000</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>305100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,52 +6669,58 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F102" s="3">
         <v>3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-29600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>30100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-27100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-71000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-108900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-188800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-147300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-78400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-60500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>673700</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-200</v>
       </c>
       <c r="R102" s="3">
         <v>-300</v>
@@ -6226,15 +6729,21 @@
         <v>-200</v>
       </c>
       <c r="T102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W102" s="3">
         <v>-300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1800</v>
       </c>
-      <c r="W102" s="3" t="s">
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>GOEV</t>
   </si>
@@ -656,129 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>600</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -810,11 +814,11 @@
         <v>0</v>
       </c>
       <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>2600</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
@@ -833,23 +837,26 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
         <v>-300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -880,12 +887,12 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,22 +911,25 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -951,12 +961,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3">
         <v>1900</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,65 +1015,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E12" s="3">
         <v>26400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>38600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>47100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>44200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>57100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>115500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>82500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>88200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>59400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>57600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>39300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>90000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19300</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,43 +1161,46 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-24500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>26700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1188,15 +1208,15 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-5000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1206,8 +1226,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1215,8 +1235,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1224,34 +1247,34 @@
         <v>3400</v>
       </c>
       <c r="E15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F15" s="3">
         <v>3200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4600</v>
       </c>
       <c r="H15" s="3">
         <v>4600</v>
       </c>
       <c r="I15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J15" s="3">
         <v>2500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2600</v>
-      </c>
-      <c r="N15" s="3">
-        <v>2100</v>
       </c>
       <c r="O15" s="3">
         <v>2100</v>
@@ -1260,25 +1283,25 @@
         <v>2100</v>
       </c>
       <c r="Q15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R15" s="3">
         <v>1900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1700</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E17" s="3">
         <v>38200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>64800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>74500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>108300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>83700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>113400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>173500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>140800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>141500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>107000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>104300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>97100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>127700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-43200</v>
       </c>
       <c r="E18" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-64400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-51400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-74500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-108300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-83700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-113400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-173500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-140800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-141500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-107000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-104300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-97100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-127700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-22100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-25100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,136 +1512,140 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>38200</v>
       </c>
       <c r="E20" s="3">
+        <v>-72500</v>
+      </c>
+      <c r="F20" s="3">
         <v>35900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-60600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>15400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>26100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>81800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>118500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-1500</v>
       </c>
       <c r="E21" s="3">
+        <v>-107300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-25200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-110500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-66300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-86200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-77700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-114300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-161500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-122700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-135500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-78800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-110500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-21500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-29200</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,8 +1658,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1647,8 +1687,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1665,15 +1705,15 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>1100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1683,8 +1723,8 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1692,79 +1732,85 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-110700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-112000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-70900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-90700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-80200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-117700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-164400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-125400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-138100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-80900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-112600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1820,22 +1866,25 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>400</v>
       </c>
       <c r="W24" s="3">
         <v>400</v>
       </c>
       <c r="X24" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-110700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-112000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-70900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-90700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-80200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-117700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-164400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-125400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-138100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-80900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-112600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-111500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-112000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-70900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-90700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-80200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-117700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-164400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-125400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-138100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-80900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-112600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-30900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-38200</v>
       </c>
       <c r="E32" s="3">
+        <v>72500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-35900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>60600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-15400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-26100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-81800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-118500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-111500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-112000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-70900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-90700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-80200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-117700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-164400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-125400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-138100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-80900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-112600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-30900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>300</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-111500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-112000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-70900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-90700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-80200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-117700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-164400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-125400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-138100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-80900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-112600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-30900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>300</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2831,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E41" s="3">
         <v>3700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>104900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>224700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>414900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>563600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>641900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>702400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1800</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,8 +2977,11 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2958,35 +3051,38 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E44" s="3">
         <v>6800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1300</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3002,8 +3098,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3029,55 +3125,58 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E45" s="3">
         <v>21900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>15200</v>
       </c>
       <c r="H45" s="3">
         <v>15200</v>
       </c>
       <c r="I45" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J45" s="3">
         <v>12800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>66600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6500</v>
-      </c>
-      <c r="R45" s="3">
-        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -3097,82 +3196,88 @@
       <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E46" s="3">
         <v>32400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>52300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>142700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>291300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>430900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>576900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>657600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>708900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3215,83 +3320,86 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>306600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>308800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>309200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>307300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>306400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>305000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>303700</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>414600</v>
+      </c>
+      <c r="E48" s="3">
         <v>416100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>413300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>405600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>400600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>367700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>350700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>330400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>302000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>250600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>216500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>155400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>103200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>59300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43300</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,8 +3412,8 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -3313,8 +3421,11 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,64 +3643,67 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E52" s="3">
         <v>96200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>96100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>95900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>96000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>93400</v>
       </c>
       <c r="I52" s="3">
         <v>93400</v>
       </c>
       <c r="J52" s="3">
+        <v>93400</v>
+      </c>
+      <c r="K52" s="3">
         <v>73900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>543300</v>
+      </c>
+      <c r="E54" s="3">
         <v>544700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>542000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>534300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>522100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>488100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>496500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>444800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>397500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>420000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>523100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>614500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>711500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>717800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>753500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>307000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>309500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>310100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>308500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>307800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>306600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>305700</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,65 +3923,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E57" s="3">
         <v>67800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>84400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>88800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>103200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>96600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>93600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>80900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>52300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>63300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>51800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17200</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
@@ -3859,40 +3990,43 @@
         <v>0</v>
       </c>
       <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E58" s="3">
         <v>66800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>54400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>32600</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>34800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3908,8 +4042,8 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3935,168 +4069,177 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E59" s="3">
         <v>66600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>64800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>63900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>85300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>85900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>80300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>86100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>52000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>83900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>64500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2700</v>
-      </c>
-      <c r="U59" s="3">
-        <v>2200</v>
       </c>
       <c r="V59" s="3">
         <v>2200</v>
       </c>
       <c r="W59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>200</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E60" s="3">
         <v>201200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>184400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>187600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>202400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>174800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>218300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>183200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>179700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>132900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>136200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>106700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>116200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E61" s="3">
         <v>28800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>68700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -4119,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>6900</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4148,55 +4291,58 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>123300</v>
+      </c>
+      <c r="E62" s="3">
         <v>130400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>79100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>112300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>63000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>61600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>41600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>33700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>39400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>42900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>46400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>72000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>64200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>153400</v>
-      </c>
-      <c r="R62" s="3">
-        <v>10200</v>
       </c>
       <c r="S62" s="3">
         <v>10200</v>
@@ -4216,11 +4362,14 @@
       <c r="X62" s="3">
         <v>10200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>347000</v>
+      </c>
+      <c r="E66" s="3">
         <v>360400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>292400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>368700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>289400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>236400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>259900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>216900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>209200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>172300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>179100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>153100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>188300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>107600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>188200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10400</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,20 +4837,23 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E70" s="3">
         <v>6500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>5600</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1597500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1592500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1481800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1453400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1341400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1270600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1179800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1099600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-981900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-817500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-692100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-554000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-473100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-360600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-345400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>188800</v>
+      </c>
+      <c r="E76" s="3">
         <v>177800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>244000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>165700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>232700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>251800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>236600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>227900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>188300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>247700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>344000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>461500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>523200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>610300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>565200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>291700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>296700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>297100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>296100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>295400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>296300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>295200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-111500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-112000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-70900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-90700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-80200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-117700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-164400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-125400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-138100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-80900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-112600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-30900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>300</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,43 +5612,44 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4600</v>
       </c>
       <c r="H83" s="3">
         <v>4600</v>
       </c>
       <c r="I83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J83" s="3">
         <v>2500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2600</v>
-      </c>
-      <c r="N83" s="3">
-        <v>2100</v>
       </c>
       <c r="O83" s="3">
         <v>2100</v>
@@ -5458,26 +5657,26 @@
       <c r="P83" s="3">
         <v>2100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>2100</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>1800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1700</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-47500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-59700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-61900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-62300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-67200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-70600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-92300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-117200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-120300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-120200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-71800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-54900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-53900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-105800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-600</v>
       </c>
       <c r="V89" s="3">
         <v>-600</v>
       </c>
       <c r="W89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X89" s="3">
         <v>-800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,70 +6158,71 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-21700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-62600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-45300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-23400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-71500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>400</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>400</v>
       </c>
       <c r="W94" s="3">
+        <v>400</v>
+      </c>
+      <c r="X94" s="3">
         <v>500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-303200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,65 +6776,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E100" s="3">
         <v>49800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>79600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>76700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>76100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>56100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>109200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>88600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>83200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>789700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-34400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>17300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>15000</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -6599,13 +6845,16 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>305100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>30100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-71000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-108900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-188800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-147300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-78400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-60500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>673700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-300</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-200</v>
       </c>
       <c r="V102" s="3">
         <v>-200</v>
       </c>
       <c r="W102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1800</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GOEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GOEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>GOEV</t>
   </si>
@@ -656,141 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -817,11 +821,11 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>2600</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
@@ -840,25 +844,28 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1800</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-300</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G9" s="3">
-        <v>500</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+        <v>1500</v>
+      </c>
+      <c r="H9" s="3">
+        <v>900</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -890,12 +897,12 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3">
         <v>700</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -914,25 +921,28 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1200</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
-        <v>700</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+        <v>-1100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-400</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -964,12 +974,12 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3">
         <v>1900</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,68 +1029,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E12" s="3">
         <v>16800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>38600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>47100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>44200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>57100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>115500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>82500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>88200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>59400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>57600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>39300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>90000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>18900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19300</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,46 +1181,49 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-24500</v>
       </c>
-      <c r="F14" s="3">
-        <v>2300</v>
-      </c>
       <c r="G14" s="3">
-        <v>3000</v>
+        <v>-69300</v>
       </c>
       <c r="H14" s="3">
+        <v>71900</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3">
-        <v>26700</v>
-      </c>
       <c r="J14" s="3">
+        <v>24200</v>
+      </c>
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1211,15 +1231,15 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-5000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1229,8 +1249,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1238,46 +1258,49 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="E15" s="3">
         <v>3400</v>
       </c>
       <c r="F15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G15" s="3">
         <v>3200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4600</v>
       </c>
       <c r="I15" s="3">
         <v>4600</v>
       </c>
       <c r="J15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K15" s="3">
         <v>2500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2600</v>
-      </c>
-      <c r="O15" s="3">
-        <v>2100</v>
       </c>
       <c r="P15" s="3">
         <v>2100</v>
@@ -1286,25 +1309,25 @@
         <v>2100</v>
       </c>
       <c r="R15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S15" s="3">
         <v>1900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1700</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E17" s="3">
         <v>43800</v>
       </c>
-      <c r="E17" s="3">
-        <v>38200</v>
-      </c>
       <c r="F17" s="3">
-        <v>64800</v>
+        <v>62600</v>
       </c>
       <c r="G17" s="3">
-        <v>51900</v>
+        <v>64300</v>
       </c>
       <c r="H17" s="3">
-        <v>74500</v>
+        <v>49300</v>
       </c>
       <c r="I17" s="3">
-        <v>108300</v>
+        <v>73600</v>
       </c>
       <c r="J17" s="3">
+        <v>81500</v>
+      </c>
+      <c r="K17" s="3">
         <v>83700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>113400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>173500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>140800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>141500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>107000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>104300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>97100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>127700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>24700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>100</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43200</v>
       </c>
-      <c r="E18" s="3">
-        <v>-38200</v>
-      </c>
       <c r="F18" s="3">
-        <v>-64400</v>
+        <v>-62600</v>
       </c>
       <c r="G18" s="3">
-        <v>-51400</v>
+        <v>-64000</v>
       </c>
       <c r="H18" s="3">
-        <v>-74500</v>
+        <v>-48800</v>
       </c>
       <c r="I18" s="3">
-        <v>-108300</v>
+        <v>-73600</v>
       </c>
       <c r="J18" s="3">
+        <v>-81500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-83700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-113400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-173500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-140800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-141500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-107000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-104300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-97100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-127700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-22100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-25100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,142 +1546,146 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>38200</v>
+        <v>-61800</v>
       </c>
       <c r="E20" s="3">
-        <v>-72500</v>
+        <v>-39800</v>
       </c>
       <c r="F20" s="3">
-        <v>35900</v>
+        <v>66900</v>
       </c>
       <c r="G20" s="3">
-        <v>-60600</v>
+        <v>35000</v>
       </c>
       <c r="H20" s="3">
-        <v>3600</v>
+        <v>-12900</v>
       </c>
       <c r="I20" s="3">
-        <v>17500</v>
+        <v>-5800</v>
       </c>
       <c r="J20" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="K20" s="3">
         <v>3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>26100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>81800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>118500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1500</v>
+        <v>22400</v>
       </c>
       <c r="E21" s="3">
-        <v>-107300</v>
+        <v>-100</v>
       </c>
       <c r="F21" s="3">
-        <v>-25200</v>
+        <v>-126200</v>
       </c>
       <c r="G21" s="3">
+        <v>-95700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-63200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-77700</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-114300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-161500</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-122700</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-135500</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-78800</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-110500</v>
       </c>
-      <c r="H21" s="3">
-        <v>-66300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-86200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-77700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-114300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-161500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-122700</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-135500</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-78800</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-110500</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-13100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-21500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-29200</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1661,37 +1698,40 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1708,15 +1748,15 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>1100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1726,8 +1766,8 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1735,105 +1775,111 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-110700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-112000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-70900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-90700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-80200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-117700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-164400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-125400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-138100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-80900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-112600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-30900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>400</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1869,22 +1915,25 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>300</v>
-      </c>
-      <c r="W24" s="3">
-        <v>400</v>
       </c>
       <c r="X24" s="3">
         <v>400</v>
       </c>
       <c r="Y24" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-110700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-112000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-70900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-90700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-80200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-117700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-164400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-125400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-138100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-80900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-112600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-30900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-111500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-29000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-112000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-70900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-90700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-80200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-117700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-164400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-125400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-138100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-80900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-112600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-23200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-30900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2468,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-38200</v>
+        <v>61800</v>
       </c>
       <c r="E32" s="3">
-        <v>72500</v>
+        <v>39800</v>
       </c>
       <c r="F32" s="3">
-        <v>-35900</v>
+        <v>-66900</v>
       </c>
       <c r="G32" s="3">
-        <v>60600</v>
+        <v>-35000</v>
       </c>
       <c r="H32" s="3">
-        <v>-3600</v>
+        <v>12900</v>
       </c>
       <c r="I32" s="3">
-        <v>-17500</v>
+        <v>5800</v>
       </c>
       <c r="J32" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-26100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-81800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-118500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6000</v>
+        <v>3300</v>
       </c>
       <c r="E33" s="3">
-        <v>-111500</v>
+        <v>-5000</v>
       </c>
       <c r="F33" s="3">
-        <v>-29000</v>
+        <v>-110700</v>
       </c>
       <c r="G33" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="H33" s="3">
         <v>-112000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-70900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-90700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-80200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-117700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-164400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-125400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-138100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-80900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-112600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-23200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-30900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>300</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6000</v>
+        <v>3300</v>
       </c>
       <c r="E35" s="3">
-        <v>-111500</v>
+        <v>-5000</v>
       </c>
       <c r="F35" s="3">
-        <v>-29000</v>
+        <v>-110700</v>
       </c>
       <c r="G35" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="H35" s="3">
         <v>-112000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-70900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-90700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-80200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-117700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-164400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-125400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-138100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-80900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-112600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-23200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-30900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>300</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,105 +2918,109 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>224700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>414900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>563600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>641900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>702400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1800</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2980,31 +3070,34 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3054,38 +3147,41 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E44" s="3">
         <v>9300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,8 +3197,8 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3128,58 +3224,61 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19500</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
-        <v>21900</v>
+        <v>2000</v>
       </c>
       <c r="F45" s="3">
-        <v>20000</v>
+        <v>600</v>
       </c>
       <c r="G45" s="3">
-        <v>18800</v>
+        <v>500</v>
       </c>
       <c r="H45" s="3">
-        <v>15200</v>
+        <v>2500</v>
       </c>
       <c r="I45" s="3">
-        <v>15200</v>
+        <v>200</v>
       </c>
       <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
         <v>12800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>66600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>100</v>
@@ -3199,108 +3298,114 @@
       <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E46" s="3">
         <v>33400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>32600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>32800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>52300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>40400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>70600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>142700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>291300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>430900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>576900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>657600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>708900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3323,86 +3428,89 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>306600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>308800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>309200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>307300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>306400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>305000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>303700</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>398900</v>
+      </c>
+      <c r="E48" s="3">
         <v>414600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>416100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>413300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>405600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>400600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>367700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>350700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>330400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>302000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>250600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>216500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>155400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>103200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>59300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3415,8 +3523,8 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3424,8 +3532,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,67 +3763,70 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>95300</v>
+        <v>66500</v>
       </c>
       <c r="E52" s="3">
-        <v>96200</v>
+        <v>66400</v>
       </c>
       <c r="F52" s="3">
-        <v>96100</v>
+        <v>66200</v>
       </c>
       <c r="G52" s="3">
-        <v>95900</v>
+        <v>66100</v>
       </c>
       <c r="H52" s="3">
-        <v>96000</v>
+        <v>65900</v>
       </c>
       <c r="I52" s="3">
+        <v>66000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>63400</v>
+      </c>
+      <c r="K52" s="3">
         <v>93400</v>
       </c>
-      <c r="J52" s="3">
-        <v>93400</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>73900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>31400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>523300</v>
+      </c>
+      <c r="E54" s="3">
         <v>543300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>544700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>542000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>534300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>522100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>488100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>496500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>444800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>397500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>420000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>523100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>614500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>711500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>717800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>753500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>307000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>309500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>310100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>308500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>307800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>306600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>305700</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,68 +4054,69 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E57" s="3">
         <v>73600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>67800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>65300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>78000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>84400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>88800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>103200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>96600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>93600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>80900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>52300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>63300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>51800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17200</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
@@ -3993,43 +4124,46 @@
         <v>0</v>
       </c>
       <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
         <v>100</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>50800</v>
+        <v>49600</v>
       </c>
       <c r="E58" s="3">
-        <v>66800</v>
+        <v>54100</v>
       </c>
       <c r="F58" s="3">
-        <v>54400</v>
+        <v>70000</v>
       </c>
       <c r="G58" s="3">
-        <v>45600</v>
+        <v>57500</v>
       </c>
       <c r="H58" s="3">
-        <v>32600</v>
+        <v>48600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>35500</v>
       </c>
       <c r="J58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K58" s="3">
         <v>34800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4045,8 +4179,8 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4072,179 +4206,188 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>70600</v>
+        <v>41600</v>
       </c>
       <c r="E59" s="3">
-        <v>66600</v>
+        <v>38500</v>
       </c>
       <c r="F59" s="3">
-        <v>64800</v>
+        <v>33000</v>
       </c>
       <c r="G59" s="3">
-        <v>63900</v>
+        <v>30300</v>
       </c>
       <c r="H59" s="3">
-        <v>85300</v>
+        <v>29700</v>
       </c>
       <c r="I59" s="3">
-        <v>85900</v>
+        <v>37800</v>
       </c>
       <c r="J59" s="3">
+        <v>43400</v>
+      </c>
+      <c r="K59" s="3">
         <v>80300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>74100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>86100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>52000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>64500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2700</v>
-      </c>
-      <c r="V59" s="3">
-        <v>2200</v>
       </c>
       <c r="W59" s="3">
         <v>2200</v>
       </c>
       <c r="X59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Y59" s="3">
         <v>100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>202300</v>
+      </c>
+      <c r="E60" s="3">
         <v>195000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>201200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>184400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>187600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>202400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>174800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>218300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>183200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>179700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>132900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>136200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>106700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>116200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>300</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28700</v>
+        <v>61800</v>
       </c>
       <c r="E61" s="3">
-        <v>28800</v>
+        <v>62800</v>
       </c>
       <c r="F61" s="3">
-        <v>28900</v>
+        <v>63700</v>
       </c>
       <c r="G61" s="3">
-        <v>68700</v>
+        <v>64600</v>
       </c>
       <c r="H61" s="3">
-        <v>24000</v>
+        <v>105200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>61300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>38100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4265,13 +4408,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>6900</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4294,58 +4437,61 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>123300</v>
+        <v>37200</v>
       </c>
       <c r="E62" s="3">
-        <v>130400</v>
+        <v>89200</v>
       </c>
       <c r="F62" s="3">
-        <v>79100</v>
+        <v>95500</v>
       </c>
       <c r="G62" s="3">
-        <v>112300</v>
+        <v>49000</v>
       </c>
       <c r="H62" s="3">
-        <v>63000</v>
+        <v>75800</v>
       </c>
       <c r="I62" s="3">
-        <v>61600</v>
+        <v>25700</v>
       </c>
       <c r="J62" s="3">
+        <v>23500</v>
+      </c>
+      <c r="K62" s="3">
         <v>41600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>33700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>39400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>42900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>46400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>72000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>64200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>153400</v>
-      </c>
-      <c r="S62" s="3">
-        <v>10200</v>
       </c>
       <c r="T62" s="3">
         <v>10200</v>
@@ -4365,11 +4511,14 @@
       <c r="Y62" s="3">
         <v>10200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>301300</v>
+      </c>
+      <c r="E66" s="3">
         <v>347000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>360400</v>
       </c>
-      <c r="F66" s="3">
-        <v>292400</v>
-      </c>
       <c r="G66" s="3">
+        <v>298000</v>
+      </c>
+      <c r="H66" s="3">
         <v>368700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>289400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>236400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>259900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>216900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>209200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>172300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>179100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>153100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>188300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>107600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>188200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10400</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,20 +5005,23 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E70" s="3">
         <v>7500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>6500</v>
       </c>
-      <c r="F70" s="3">
-        <v>5600</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1594200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1597500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1592500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1481800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1453400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1341400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1270600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1179800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1099600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-981900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-817500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-692100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-554000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-473100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-360600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-345400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>300</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>213200</v>
+      </c>
+      <c r="E76" s="3">
         <v>188800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>177800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>244000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>165700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>232700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>251800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>236600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>227900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>188300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>247700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>344000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>461500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>523200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>610300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>565200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>291700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>296700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>297100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>296100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>295400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>296300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>295200</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6000</v>
+        <v>3300</v>
       </c>
       <c r="E81" s="3">
-        <v>-111500</v>
+        <v>-5000</v>
       </c>
       <c r="F81" s="3">
-        <v>-29000</v>
+        <v>-110700</v>
       </c>
       <c r="G81" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="H81" s="3">
         <v>-112000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-70900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-90700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-80200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-117700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-164400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-125400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-138100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-80900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-112600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-23200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-30900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>300</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,46 +5811,47 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H83" s="3">
         <v>3500</v>
       </c>
-      <c r="E83" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>4600</v>
-      </c>
       <c r="I83" s="3">
-        <v>4600</v>
+        <v>2900</v>
       </c>
       <c r="J83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K83" s="3">
         <v>2500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>2100</v>
       </c>
       <c r="P83" s="3">
         <v>2100</v>
@@ -5660,26 +5859,26 @@
       <c r="Q83" s="3">
         <v>2100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>2100</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>1800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1700</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-35900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-47500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-59700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-61900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-62300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-67200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-70600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-92300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-117200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-120300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-120200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-71800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-54900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-53900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-105800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-600</v>
       </c>
       <c r="W89" s="3">
         <v>-600</v>
       </c>
       <c r="X89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,73 +6379,74 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-21700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-37000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-62600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-45300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6608,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-71500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W94" s="3">
         <v>400</v>
       </c>
       <c r="X94" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y94" s="3">
         <v>500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-303200</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,31 +6716,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,68 +7022,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E100" s="3">
         <v>38800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>49800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>79600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>76700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>76100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>56100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>109200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>88600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>83200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>789700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-34400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>17300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>15000</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -6848,36 +7094,39 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>305100</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6927,78 +7176,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-29600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-71000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-108900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-188800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-147300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-78400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-60500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>673700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-300</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-200</v>
       </c>
       <c r="W102" s="3">
         <v>-200</v>
       </c>
       <c r="X102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1800</v>
       </c>
-      <c r="Z102" s="3" t="s">
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
